--- a/healthcare_surveys/028_medication_dispensing_feedback_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/028_medication_dispensing_feedback_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'doctor_visit',_'value':_'doctor'}</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'doctor_visit', 'value': 'Doctor'}</t>
+          <t>Doctor</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'pharmacy_visit',_'value':_'pharmacy'}</t>
+          <t>pharmacy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'pharmacy_visit', 'value': 'Pharmacy'}</t>
+          <t>Pharmacy</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'both_doctor_and_pharmacy',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'both_doctor_and_pharmacy', 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'on_time',_'value':_'on_time'}</t>
+          <t>on_time</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'on_time', 'value': 'On Time'}</t>
+          <t>On Time</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'before_expected',_'value':_'before_expected'}</t>
+          <t>before_expected</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'before_expected', 'value': 'Before Expected'}</t>
+          <t>Before Expected</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'after_expected',_'value':_'after_expected'}</t>
+          <t>after_expected</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'after_expected', 'value': 'After Expected'}</t>
+          <t>After Expected</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_clear',_'value':_'very_clear'}</t>
+          <t>very_clear</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'very_clear', 'value': 'Very Clear'}</t>
+          <t>Very Clear</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_clear',_'value':_'somewhat_clear'}</t>
+          <t>somewhat_clear</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'somewhat_clear', 'value': 'Somewhat Clear'}</t>
+          <t>Somewhat Clear</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_clear_at_all',_'value':_'not_clear_at_all'}</t>
+          <t>not_clear_at_all</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_clear_at_all', 'value': 'Not Clear At All'}</t>
+          <t>Not Clear At All</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'excellent',_'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'excellent', 'value': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'bad',_'value':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'bad', 'value': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'follow_up_yes',_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'follow_up_yes', 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'follow_up_no',_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'follow_up_no', 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
